--- a/src/Excelsior.Tests/ComplexTypeWithCustomEnumerableRender.Null.verified.xlsx
+++ b/src/Excelsior.Tests/ComplexTypeWithCustomEnumerableRender.Null.verified.xlsx
@@ -80,7 +80,7 @@
 </file>
 
 <file path=customXml/item.xml><?xml version="1.0" encoding="utf-8"?>
-<columnMetadata xmlns="https://github.com/Papyrine/Excelsior/columnMetadata/v1">
+<columnMetadata xmlns="https://github.com/SimonCropp/Excelsior/columnMetadata/v1">
   <sheet name="Sheet1">
     <column index="1" property="Name"/>
     <column index="2" property="Addresses"/>
